--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,225 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>60000</v>
+      </c>
+      <c r="E8" s="3">
         <v>67500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>58500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>65000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>54200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>43600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>41700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>40400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>74300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>36300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>43400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>38900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E9" s="3">
         <v>34900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E10" s="3">
         <v>32600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>32700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>28400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>42900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -892,8 +904,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -939,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1052,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1102,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1121,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E17" s="3">
         <v>37800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E18" s="3">
         <v>29700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>23500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>29900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>25600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>36300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>21400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,55 +1241,59 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>17500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-60900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-14300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-20600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-11600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>41400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>32100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>25500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1303,8 +1339,11 @@
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,85 +1389,91 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>47200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>28000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>34000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>77700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>49700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>47500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1436,16 +1481,19 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1539,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>47500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>34000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>25100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>77700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>47200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>47500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-31000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>34000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>25100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>77700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>49700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>47200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1839,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-17500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>60900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>14300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>20600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>11600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-41400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-32100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-25500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>47500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-31000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>25100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>77700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>49700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>47200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1989,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>47500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-31000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>25100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>77700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>49700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>47200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,55 +2136,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>96000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>82700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,55 +2234,61 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>40200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2239,55 +2334,61 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>800</v>
       </c>
       <c r="H45" s="3">
         <v>800</v>
       </c>
       <c r="I45" s="3">
+        <v>800</v>
+      </c>
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>500</v>
       </c>
       <c r="L45" s="3">
         <v>500</v>
       </c>
       <c r="M45" s="3">
+        <v>500</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2333,55 +2434,61 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1991000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1885300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1821700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1750700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1786600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1834000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1827400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1776600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1775600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1767600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1744300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1638700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1586900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1588600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2427,8 +2534,11 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2474,8 +2584,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2684,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2615,8 +2734,11 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,55 +2784,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2001700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1896300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1834800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1854500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1872400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1885700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1874800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1805000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1782700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1789900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1755300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1681300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1614800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1603100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,55 +2876,59 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E57" s="3">
         <v>11200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>36900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>20100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2841,55 +2974,61 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E59" s="3">
         <v>24200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>36400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2935,55 +3074,61 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1081700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1000200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>976700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1002400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>951300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>950500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>939700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>867400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>822400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>796700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>796000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>716300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>720000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>719400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3029,8 +3174,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,55 +3324,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1122200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1035600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>998400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1024200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>988800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>970800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>969500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>882600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>852200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>848900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>829400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>768300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>736500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>735900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,55 +3594,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-153500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-175200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-201400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-210700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-161000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-138400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-154800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-137600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-129500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-119000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-129100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-142100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-176800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-191500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,55 +3794,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>879600</v>
+      </c>
+      <c r="E76" s="3">
         <v>860800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>836400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>830300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>883600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>914900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>905200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>922500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>930500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>941000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>925900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>912900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>878300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>867200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3894,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>47500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-31000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>25100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>77700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>49700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>47200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4021,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3871,8 +4069,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4319,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-36000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>65000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-63000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4219,8 +4439,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4539,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4360,8 +4589,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,55 +4611,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-18600</v>
+        <v>-21200</v>
       </c>
       <c r="E96" s="3">
         <v>-18600</v>
       </c>
       <c r="F96" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="G96" s="3">
         <v>-33600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-17100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-15900</v>
       </c>
       <c r="J96" s="3">
         <v>-15900</v>
       </c>
       <c r="K96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="L96" s="3">
         <v>-26500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-10000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-19600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-9700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-21000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4809,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E100" s="3">
         <v>2100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>13000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-25900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>55500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>28400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-10000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>44600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-19400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,51 +4909,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-84500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>39100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,237 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E8" s="3">
         <v>60000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>58500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>65000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>54200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>43600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>40400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>74300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>36300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>43400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>38900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E9" s="3">
         <v>35500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>34900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>31400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E10" s="3">
         <v>24500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>32600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>26500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>42900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -905,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -955,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,8 +1022,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1055,8 +1075,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1105,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E17" s="3">
         <v>38200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>37800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>38000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E18" s="3">
         <v>21800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>29700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>23500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>36300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>21400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,58 +1275,62 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-26200</v>
       </c>
       <c r="E20" s="3">
+        <v>29200</v>
+      </c>
+      <c r="F20" s="3">
         <v>17500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-60900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-14300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-20600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>41400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>32100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1342,8 +1379,11 @@
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1392,91 +1432,97 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
+      <c r="D23" s="3">
+        <v>6500</v>
       </c>
       <c r="E23" s="3">
+        <v>51100</v>
+      </c>
+      <c r="F23" s="3">
         <v>47200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>34000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>77700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>49700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>47500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>31100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1484,16 +1530,19 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>6400</v>
       </c>
       <c r="E26" s="3">
+        <v>51000</v>
+      </c>
+      <c r="F26" s="3">
         <v>47500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>34000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>77700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>47200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>6400</v>
       </c>
       <c r="E27" s="3">
+        <v>51000</v>
+      </c>
+      <c r="F27" s="3">
         <v>47500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>34000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>77700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>49700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>47200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>26200</v>
       </c>
       <c r="E32" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-17500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>60900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>14300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>20600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-41400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-32100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>6400</v>
       </c>
       <c r="E33" s="3">
+        <v>51000</v>
+      </c>
+      <c r="F33" s="3">
         <v>47500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>77700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>49700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>47200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>6400</v>
       </c>
       <c r="E35" s="3">
+        <v>51000</v>
+      </c>
+      <c r="F35" s="3">
         <v>47500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>77700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>49700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>47200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E41" s="3">
         <v>8400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>96000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2237,58 +2327,64 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>19700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>40200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2337,58 +2433,64 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>800</v>
       </c>
       <c r="I45" s="3">
         <v>800</v>
       </c>
       <c r="J45" s="3">
+        <v>800</v>
+      </c>
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>500</v>
       </c>
       <c r="M45" s="3">
         <v>500</v>
       </c>
       <c r="N45" s="3">
+        <v>500</v>
+      </c>
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2437,58 +2539,64 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1907200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1991000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1885300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1821700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1750700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1786600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1834000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1827400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1776600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1775600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1767600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1744300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1638700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1586900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1588600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2537,8 +2645,11 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2587,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,8 +2804,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2737,8 +2857,11 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1968300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2001700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1896300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1834800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1854500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1872400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1885700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1874800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1805000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1782700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1789900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1755300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1681300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1614800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1603100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,58 +3007,62 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E57" s="3">
         <v>5700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2977,58 +3111,64 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E59" s="3">
         <v>34700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3077,58 +3217,64 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1060500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1081700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1000200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>976700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1002400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>951300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>950500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>939700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>867400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>822400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>796700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>796000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>716300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>720000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>719400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3177,8 +3323,11 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1105200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1122200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1035600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>998400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1024200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>988800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>970800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>969500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>882600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>852200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>848900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>829400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>768300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>736500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>735900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-165400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-153500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-175200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-201400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-210700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-161000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-138400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-154800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-137600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-129500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-119000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-129100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-142100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-176800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-191500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>863100</v>
+      </c>
+      <c r="E76" s="3">
         <v>879600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>860800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>836400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>830300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>883600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>914900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>905200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>922500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>930500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>941000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>925900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>912900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>878300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>867200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>6400</v>
       </c>
       <c r="E81" s="3">
+        <v>51000</v>
+      </c>
+      <c r="F81" s="3">
         <v>47500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>77700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>49700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>47200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4072,8 +4271,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-54600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-36000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>65000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-63000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>51900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4612,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4442,8 +4663,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4592,8 +4822,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,58 +4845,62 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-21200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-18600</v>
       </c>
       <c r="F96" s="3">
         <v>-18600</v>
       </c>
       <c r="G96" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="H96" s="3">
         <v>-33600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-17100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-15900</v>
       </c>
       <c r="K96" s="3">
         <v>-15900</v>
       </c>
       <c r="L96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="M96" s="3">
         <v>-26500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-10000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-19600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-9700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,58 +5055,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="E100" s="3">
         <v>56200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-48500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-25900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>55500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>28400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>44600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-19400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-27300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4912,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-84500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>39100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E8" s="3">
         <v>73600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>60000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>67500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>58500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>65000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>54200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>43600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>41700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>40400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>36300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>38900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E9" s="3">
         <v>38100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>35500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>32000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>32300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>31400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E10" s="3">
         <v>35500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>32600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>32700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>23000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>42900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>21000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E17" s="3">
         <v>41000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>31300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>38000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E18" s="3">
         <v>32600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>21800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>29700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>29900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>24200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>25600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>21400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,61 +1309,65 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-26200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>29200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>17500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-60900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-14300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>41400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>32100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>25500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1382,8 +1419,11 @@
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1435,61 +1475,67 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E23" s="3">
         <v>6500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>47200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>28000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>34000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>77700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>49700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>47500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>31100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1497,35 +1543,35 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1533,16 +1579,19 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E26" s="3">
         <v>6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>51000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>47500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>27900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>34000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>25100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>77700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>47200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E27" s="3">
         <v>6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>51000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>47500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>34000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>25100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>77700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>49700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>47200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>600</v>
+      </c>
+      <c r="E32" s="3">
         <v>26200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-29200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-17500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>60900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>14300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-41400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-32100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-25500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E33" s="3">
         <v>6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>51000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>47500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>34000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>25100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>77700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>49700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>47200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E35" s="3">
         <v>6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>51000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>47500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>34000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>25100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>77700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>49700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>47200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E41" s="3">
         <v>48500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>96000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,61 +2420,67 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E43" s="3">
         <v>11500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>40200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2436,61 +2532,67 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>800</v>
       </c>
       <c r="J45" s="3">
         <v>800</v>
       </c>
       <c r="K45" s="3">
+        <v>800</v>
+      </c>
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>500</v>
       </c>
       <c r="N45" s="3">
         <v>500</v>
       </c>
       <c r="O45" s="3">
+        <v>500</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2542,61 +2644,67 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1947000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1907200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1991000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1885300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1821700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1750700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1786600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1834000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1827400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1776600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1775600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1767600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1744300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1638700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1586900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1588600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2648,8 +2756,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,8 +2924,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1960500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1968300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2001700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1896300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1834800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1854500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1872400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1885700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1874800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1805000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1782700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1789900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1755300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1681300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1614800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1603100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,61 +3138,65 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E57" s="3">
         <v>21800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3114,61 +3248,67 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E59" s="3">
         <v>23000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>34700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>36400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3220,61 +3360,67 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1061700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1060500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1081700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1000200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>976700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1002400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>951300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>950500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>939700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>867400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>822400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>796700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>796000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>716300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>720000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>719400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1099700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1105200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1122200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1035600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>998400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1024200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>988800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>970800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>969500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>882600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>852200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>848900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>829400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>768300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>736500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>735900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-164900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-165400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-153500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-175200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-201400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-210700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-161000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-138400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-154800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-137600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-129500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-119000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-129100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-142100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-176800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-191500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>860800</v>
+      </c>
+      <c r="E76" s="3">
         <v>863100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>879600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>860800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>836400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>830300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>883600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>914900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>905200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>922500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>930500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>941000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>925900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>912900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>878300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>867200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E81" s="3">
         <v>6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>51000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>47500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>34000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>25100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>77700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>49700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>47200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4274,8 +4473,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="E89" s="3">
         <v>96400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-54600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-36000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>65000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-63000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>51900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>29900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4666,8 +4887,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,8 +4999,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4825,8 +5055,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,61 +5079,65 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E96" s="3">
         <v>-29100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-21200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-18600</v>
       </c>
       <c r="G96" s="3">
         <v>-18600</v>
       </c>
       <c r="H96" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="I96" s="3">
         <v>-33600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-17100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-15900</v>
       </c>
       <c r="L96" s="3">
         <v>-15900</v>
       </c>
       <c r="M96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="N96" s="3">
         <v>-26500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-10000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-19600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-21000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-6300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,61 +5301,67 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-56300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-48500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>55500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>28400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>44600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-27300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="E102" s="3">
         <v>40100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-84500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>39100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E8" s="3">
         <v>61400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>73600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>60000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>58500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>65000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>55500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>54200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>43600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>40400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>74300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>36300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>43400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>38900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>35500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>38100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>35500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>34900</v>
-      </c>
-      <c r="H9" s="3">
-        <v>32000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>32300</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>28800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>25800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>25900</v>
+        <v>59600</v>
       </c>
       <c r="E10" s="3">
-        <v>35500</v>
+        <v>61400</v>
       </c>
       <c r="F10" s="3">
-        <v>24500</v>
+        <v>73600</v>
       </c>
       <c r="G10" s="3">
-        <v>32600</v>
+        <v>60000</v>
       </c>
       <c r="H10" s="3">
-        <v>26500</v>
+        <v>67500</v>
       </c>
       <c r="I10" s="3">
-        <v>32700</v>
+        <v>58500</v>
       </c>
       <c r="J10" s="3">
+        <v>65000</v>
+      </c>
+      <c r="K10" s="3">
         <v>26700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>42900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,31 +1062,34 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>26100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-29200</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-17500</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-4500</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>60900</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>38400</v>
+        <v>14500</v>
       </c>
       <c r="E17" s="3">
-        <v>41000</v>
+        <v>14600</v>
       </c>
       <c r="F17" s="3">
-        <v>38200</v>
+        <v>16700</v>
       </c>
       <c r="G17" s="3">
-        <v>37800</v>
+        <v>14200</v>
       </c>
       <c r="H17" s="3">
-        <v>35000</v>
+        <v>16000</v>
       </c>
       <c r="I17" s="3">
-        <v>35100</v>
+        <v>14500</v>
       </c>
       <c r="J17" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K17" s="3">
         <v>31300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>23000</v>
+        <v>45100</v>
       </c>
       <c r="E18" s="3">
-        <v>32600</v>
+        <v>46700</v>
       </c>
       <c r="F18" s="3">
-        <v>21800</v>
+        <v>56900</v>
       </c>
       <c r="G18" s="3">
-        <v>29700</v>
+        <v>45800</v>
       </c>
       <c r="H18" s="3">
-        <v>23500</v>
+        <v>51500</v>
       </c>
       <c r="I18" s="3">
-        <v>29900</v>
+        <v>44000</v>
       </c>
       <c r="J18" s="3">
+        <v>49200</v>
+      </c>
+      <c r="K18" s="3">
         <v>24200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,87 +1343,91 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-26200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>29200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>17500</v>
-      </c>
-      <c r="H20" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-60900</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-14300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-20600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-11600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>41400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>32100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>25500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>56900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>45800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>51500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>44000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>49200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1422,31 +1459,34 @@
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>23800</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>51100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>28000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>25100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>77700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>49700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>47500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>31100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1546,35 +1592,35 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1582,16 +1628,19 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E26" s="3">
         <v>22400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>47500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>27900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>77700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>47200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
         <v>22400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>47500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>27900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>25100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>77700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>49700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>47200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>26200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-29200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-17500</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>60900</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>14300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>20600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>11600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-41400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-32100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-25500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
         <v>22400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>47500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>27900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>25100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>77700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>49700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>47200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
         <v>22400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>47500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>27900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>25100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>77700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>49700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>47200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E41" s="3">
         <v>9800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>48500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>96000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,87 +2513,93 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2800</v>
+        <v>78100</v>
       </c>
       <c r="E43" s="3">
-        <v>11500</v>
+        <v>43600</v>
       </c>
       <c r="F43" s="3">
-        <v>1000</v>
+        <v>47800</v>
       </c>
       <c r="G43" s="3">
+        <v>37700</v>
+      </c>
+      <c r="H43" s="3">
+        <v>43100</v>
+      </c>
+      <c r="I43" s="3">
+        <v>34200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>30600</v>
+      </c>
+      <c r="K43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="M43" s="3">
         <v>2700</v>
       </c>
-      <c r="H43" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>3200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>7100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>2700</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>19700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>40200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2535,87 +2631,93 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>800</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>800</v>
       </c>
       <c r="L45" s="3">
+        <v>800</v>
+      </c>
+      <c r="M45" s="3">
         <v>2100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>500</v>
       </c>
       <c r="O45" s="3">
         <v>500</v>
       </c>
       <c r="P45" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>109400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>54300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>97400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>47500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>51500</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>131100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2647,87 +2749,93 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1947000</v>
+        <v>1806200</v>
       </c>
       <c r="E47" s="3">
-        <v>1907200</v>
+        <v>1906100</v>
       </c>
       <c r="F47" s="3">
-        <v>1991000</v>
+        <v>1870800</v>
       </c>
       <c r="G47" s="3">
-        <v>1885300</v>
+        <v>1954300</v>
       </c>
       <c r="H47" s="3">
-        <v>1821700</v>
+        <v>1844900</v>
       </c>
       <c r="I47" s="3">
-        <v>1750700</v>
+        <v>1788500</v>
       </c>
       <c r="J47" s="3">
+        <v>1723400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1786600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1834000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1827400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1776600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1775600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1767600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1744300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1638700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1586900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1588600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2759,8 +2867,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,31 +3044,34 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1915600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1960500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1968300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2001700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1896300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1834800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1854500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1872400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1885700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1874800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1805000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1782700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1789900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1755300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1681300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1614800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1603100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3269,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>12800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>41100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3213,13 +3347,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3251,87 +3385,93 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25100</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>23000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>34700</v>
+        <v>2700</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G59" s="3">
-        <v>24200</v>
+        <v>10800</v>
       </c>
       <c r="H59" s="3">
-        <v>20300</v>
+        <v>2800</v>
       </c>
       <c r="I59" s="3">
-        <v>20700</v>
-      </c>
-      <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>36400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>44800</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>40500</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>65400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>21700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>146800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3363,87 +3503,93 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1054900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1061700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1060500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1081700</v>
       </c>
-      <c r="G61" s="3">
-        <v>1000200</v>
-      </c>
       <c r="H61" s="3">
+        <v>970200</v>
+      </c>
+      <c r="I61" s="3">
         <v>976700</v>
       </c>
-      <c r="I61" s="3">
-        <v>1002400</v>
-      </c>
       <c r="J61" s="3">
+        <v>877400</v>
+      </c>
+      <c r="K61" s="3">
         <v>951300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>950500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>939700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>867400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>822400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>796700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>796000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>716300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>720000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>719400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1076400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1099700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1105200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1122200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1035600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>998400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1024200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>988800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>970800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>969500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>882600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>852200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>848900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>829400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>768300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>736500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>735900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-184600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-164900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-165400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-153500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-175200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-201400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-210700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-161000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-138400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-154800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-137600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-129500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-119000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-129100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-142100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-176800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-191500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>839200</v>
+      </c>
+      <c r="E76" s="3">
         <v>860800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>863100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>879600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>860800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>836400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>830300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>883600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>914900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>905200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>922500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>930500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>941000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>925900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>912900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>878300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>867200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
         <v>22400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>47500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>27900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>25100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>77700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>49700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>47200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,31 +4618,32 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>96400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-54600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-36000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>29900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,31 +5054,32 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,31 +5229,34 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -5058,8 +5288,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,64 +5313,68 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-19300</v>
+        <v>21900</v>
       </c>
       <c r="E96" s="3">
-        <v>-29100</v>
+        <v>19300</v>
       </c>
       <c r="F96" s="3">
-        <v>-21200</v>
+        <v>29100</v>
       </c>
       <c r="G96" s="3">
-        <v>-18600</v>
+        <v>21200</v>
       </c>
       <c r="H96" s="3">
-        <v>-18600</v>
+        <v>18600</v>
       </c>
       <c r="I96" s="3">
-        <v>-33600</v>
+        <v>18600</v>
       </c>
       <c r="J96" s="3">
+        <v>33600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-17100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-15900</v>
       </c>
       <c r="M96" s="3">
         <v>-15900</v>
       </c>
       <c r="N96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="O96" s="3">
         <v>-26500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-10000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-9700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-21000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-6300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,87 +5547,93 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-56300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>56200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-48500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>55500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>28400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>44600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-19400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-36200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-27300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-38700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>40100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-84500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>13700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,158 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E8" s="3">
         <v>59600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>61400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>73600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>60000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>67500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>58500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>65000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>55500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>54200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>43600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>40400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>42600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>74300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>36300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>43400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>38900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -832,100 +838,106 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>28800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>25800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E10" s="3">
         <v>59600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>61400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>73600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>60000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>67500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>58500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>65000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>26700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>28400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>22500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>42900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>21000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +959,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1019,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,35 +1081,38 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E14" s="3">
         <v>22000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>26100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-29200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-17500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>60900</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1124,8 +1143,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E17" s="3">
         <v>14500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E18" s="3">
         <v>45100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>56900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>51500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>44000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>49200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1376,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1370,68 +1403,71 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-14300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-20600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-11600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>41400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>32100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>25500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>9700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E21" s="3">
         <v>45100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>46700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>56900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>45800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>51500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>44000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1462,35 +1498,38 @@
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E22" s="3">
         <v>23600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>21800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19300</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1521,72 +1560,78 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>51100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>28000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>16300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>25100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>77700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>49700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>47500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>31100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1595,35 +1640,35 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1631,16 +1676,19 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>51000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>47500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>27900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>34000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>77700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>49700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>47200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>47500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>27900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>34000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>25100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>77700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>49700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>47200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2118,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2078,100 +2147,106 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>14300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>20600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>11600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-41400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-32100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-25500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-9700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>51000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>47500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>27900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>34000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>25100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>77700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>49700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>47200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>31100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>51000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>47500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>27900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>34000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>25100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>77700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>49700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>47200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>31100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E41" s="3">
         <v>29800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>48500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>96000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,67 +2605,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E43" s="3">
         <v>78100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>43600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>47800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>37700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>43100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>34200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>30600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>19700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>40200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2601,8 +2696,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2634,8 +2729,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2660,68 +2758,71 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>800</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L45" s="3">
         <v>800</v>
       </c>
       <c r="M45" s="3">
+        <v>800</v>
+      </c>
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3600</v>
-      </c>
-      <c r="O45" s="3">
-        <v>500</v>
       </c>
       <c r="P45" s="3">
         <v>500</v>
       </c>
       <c r="Q45" s="3">
+        <v>500</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E46" s="3">
         <v>109400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>54300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>97400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>51500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>46300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>131100</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2752,67 +2853,73 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1888700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1806200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1906100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1870800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1954300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1844900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1788500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1723400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1786600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1834000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1827400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1776600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1775600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1767600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1744300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1638700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1586900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1588600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2837,8 +2944,8 @@
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -2870,8 +2977,11 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2929,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3163,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3073,8 +3192,8 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3106,8 +3225,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1945700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1915600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1960500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1968300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2001700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1896300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1834800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1854500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1872400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1885700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1874800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1805000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1782700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1789900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1755300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1681300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1614800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1603100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,67 +3399,71 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3347,17 +3480,17 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>30000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>125000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3388,94 +3521,100 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
         <v>10800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>36400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E60" s="3">
         <v>21500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>38000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>40500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>21700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>146800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3506,67 +3645,73 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1099200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1054900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1061700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1060500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1081700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>970200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>976700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>877400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>951300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>950500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>939700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>867400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>822400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>796700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>796000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>716300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>720000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>719400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3591,8 +3736,8 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3624,8 +3769,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1124900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1076400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1099700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1105200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1122200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1035600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>998400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1024200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>988800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>970800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>969500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>882600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>852200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>848900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>829400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>768300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>736500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>735900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-200900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-184600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-164900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-165400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-153500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-175200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-201400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-210700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-161000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-138400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-154800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-137600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-129500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-119000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-129100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-142100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-176800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-191500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>820800</v>
+      </c>
+      <c r="E76" s="3">
         <v>839200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>860800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>863100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>879600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>860800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>836400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>830300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>883600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>914900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>905200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>922500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>930500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>941000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>925900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>912900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>878300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>867200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>51000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>47500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>27900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>34000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>25100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>77700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>49700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>47200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>31100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4816,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4645,8 +4843,8 @@
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -4678,8 +4876,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E89" s="3">
         <v>52000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>96400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-54600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-36000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>65000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-63000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>51900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>29900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,8 +5274,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5081,8 +5301,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5114,8 +5334,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,8 +5458,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5258,8 +5487,8 @@
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -5291,8 +5520,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,67 +5546,71 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E96" s="3">
         <v>21900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>19300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>29100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>21200</v>
-      </c>
-      <c r="H96" s="3">
-        <v>18600</v>
       </c>
       <c r="I96" s="3">
         <v>18600</v>
       </c>
       <c r="J96" s="3">
+        <v>18600</v>
+      </c>
+      <c r="K96" s="3">
         <v>33600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-17100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-15900</v>
       </c>
       <c r="N96" s="3">
         <v>-15900</v>
       </c>
       <c r="O96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="P96" s="3">
         <v>-26500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-19600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-9700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-21000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-6300</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,67 +5792,73 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-32000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-56300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>56200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-48500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>55500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>28400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>44600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-19400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-27300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5635,8 +5883,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5668,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E102" s="3">
         <v>20000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-38700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>40100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-84500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,164 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E8" s="3">
         <v>57900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>59600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>61400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>73600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>60000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>58500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>43600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>41700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>40400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>42600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>74300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>36300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>43400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -841,103 +848,109 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>28800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>25800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E10" s="3">
         <v>57900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>59600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>61400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>73600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>60000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>58500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>21500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>42900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>21000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1022,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,38 +1101,41 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E14" s="3">
         <v>13200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>26100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-29200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-17500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>60900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1146,8 +1166,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,8 +1255,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1238,123 +1265,129 @@
         <v>13800</v>
       </c>
       <c r="E17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F17" s="3">
         <v>14500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E18" s="3">
         <v>44000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>45100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>56900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>44000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>49200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>36300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>21400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1406,71 +1440,74 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-14300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-20600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>41400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>32100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>25500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E21" s="3">
         <v>44000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>45100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>46700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>56900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>45800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>51500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>44000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>49200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1501,38 +1538,41 @@
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E22" s="3">
         <v>25200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>21800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19300</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1563,79 +1603,85 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E23" s="3">
         <v>5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>51100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>47200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>28000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>77700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>49700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>47500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>31100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1643,35 +1689,35 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1679,16 +1725,19 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E26" s="3">
         <v>5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>22400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>51000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>47500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>27900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>77700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>49700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>47200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E27" s="3">
         <v>5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>22400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>47500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>27900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>34000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>25100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>77700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>49700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>47200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>31100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2150,103 +2220,109 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>14300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>20600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-41400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-32100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-25500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E33" s="3">
         <v>5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>22400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>51000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>47500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>27900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>34000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>25100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>77700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>49700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>47200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>31100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E35" s="3">
         <v>5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>22400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>51000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>47500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>27900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>34000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>25100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>77700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>49700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>47200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>31100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,8 +2570,9 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2493,61 +2580,64 @@
         <v>7700</v>
       </c>
       <c r="E41" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F41" s="3">
         <v>29800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>48500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>96000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>82700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>43700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,70 +2698,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E43" s="3">
         <v>48100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>78100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>43600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>43100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>34200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>19700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>40200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2699,8 +2795,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2732,8 +2828,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2761,71 +2860,74 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
-        <v>800</v>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M45" s="3">
         <v>800</v>
       </c>
       <c r="N45" s="3">
+        <v>800</v>
+      </c>
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>500</v>
       </c>
       <c r="Q45" s="3">
         <v>500</v>
       </c>
       <c r="R45" s="3">
+        <v>500</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E46" s="3">
         <v>57000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>109400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>47500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>51500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>131100</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2856,70 +2958,76 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1845700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1888700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1806200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1906100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1870800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1954300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1844900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1788500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1723400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1786600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1834000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1827400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1776600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1775600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1767600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1744300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1638700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1586900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1588600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2947,8 +3055,8 @@
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -2980,8 +3088,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3283,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3195,8 +3315,8 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1896300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1945700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1915600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1960500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1968300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2001700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1896300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1834800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1854500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1872400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1885700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1874800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1805000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1782700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1789900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1755300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1681300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1614800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1603100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,70 +3530,74 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>36900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3483,17 +3617,17 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>30000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>125000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3524,100 +3658,106 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>10800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>36400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E60" s="3">
         <v>25700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>21500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>21700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>146800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3648,70 +3788,76 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1099800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1099200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1054900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1061700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1060500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1081700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>970200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>976700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>877400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>951300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>950500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>939700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>867400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>822400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>796700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>796000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>716300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>720000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>719400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3739,8 +3885,8 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1139500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1124900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1076400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1099700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1105200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1122200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1035600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>998400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1024200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>988800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>970800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>969500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>882600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>852200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>848900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>829400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>768300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>736500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>735900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-262800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-200900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-184600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-164900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-165400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-153500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-175200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-201400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-210700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-161000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-138400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-154800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-137600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-129500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-119000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-129100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-142100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-176800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-191500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>756800</v>
+      </c>
+      <c r="E76" s="3">
         <v>820800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>839200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>860800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>863100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>879600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>860800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>836400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>830300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>883600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>914900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>905200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>922500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>930500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>941000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>925900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>912900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>878300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>867200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E81" s="3">
         <v>5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>22400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>51000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>47500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>27900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>34000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>25100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>77700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>49700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>47200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>31100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4846,8 +5045,8 @@
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-43400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>52000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>96400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-54600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-36000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>65000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-63000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>51900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>29900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5304,8 +5525,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5337,8 +5558,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5688,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5490,8 +5720,8 @@
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -5523,8 +5753,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,70 +5780,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E96" s="3">
         <v>19200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>21900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>19300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>29100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>21200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>18600</v>
       </c>
       <c r="J96" s="3">
         <v>18600</v>
       </c>
       <c r="K96" s="3">
+        <v>18600</v>
+      </c>
+      <c r="L96" s="3">
         <v>33600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-17100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-15900</v>
       </c>
       <c r="O96" s="3">
         <v>-15900</v>
       </c>
       <c r="P96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-10000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-19600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-9700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-21000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-6300</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E100" s="3">
         <v>21300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-32000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-22000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-56300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-48500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>55500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>28400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>44600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-36200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-27300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5886,8 +6135,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-38700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>40100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-84500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>39100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>25000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,171 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E8" s="3">
         <v>56100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>59600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>61400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>73600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>60000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>58500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>55500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>54200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>43600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>41700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>40400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>42600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>74300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>43400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -851,106 +858,112 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>28800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>25800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E10" s="3">
         <v>56100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>57900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>59600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>61400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>73600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>60000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>58500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>65000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>42900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>21000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>24000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,41 +1121,44 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E14" s="3">
         <v>62000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>22000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>26100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-29200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-17500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>60900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1169,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13800</v>
+        <v>12700</v>
       </c>
       <c r="E17" s="3">
         <v>13800</v>
       </c>
       <c r="F17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="G17" s="3">
         <v>14500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E18" s="3">
         <v>42300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>44000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>45100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>56900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>51500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>44000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>49200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>18700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>36300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>21400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1443,74 +1477,77 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-14300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-20600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>41400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>32100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>25500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E21" s="3">
         <v>42300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>44000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>46700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>56900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>51500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>44000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>49200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1541,41 +1578,44 @@
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E22" s="3">
         <v>23000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19300</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1606,85 +1646,91 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-42700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>51100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>47200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>28000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>34000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>25100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>77700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>49700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>47500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>31100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1692,35 +1738,35 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1728,16 +1774,19 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>51000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>47500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>77700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>49700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>47200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>31100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>22400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>51000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>47500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>25100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>77700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>47200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>31100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2223,106 +2293,112 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>14300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>20600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-41400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-32100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-25500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>22400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>51000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>47500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>25100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>77700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>49700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>47200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>31100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>22400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>51000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>47500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>25100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>77700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>49700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>47200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>31100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7700</v>
+        <v>6500</v>
       </c>
       <c r="E41" s="3">
         <v>7700</v>
       </c>
       <c r="F41" s="3">
+        <v>7700</v>
+      </c>
+      <c r="G41" s="3">
         <v>29800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>48500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>96000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>42500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,73 +2791,79 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E43" s="3">
         <v>41900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>78100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>43600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>37700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>43100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>34200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>30600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>19700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>40200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2798,8 +2894,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2831,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2863,74 +2962,77 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
-        <v>800</v>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N45" s="3">
         <v>800</v>
       </c>
       <c r="O45" s="3">
+        <v>800</v>
+      </c>
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>500</v>
       </c>
       <c r="R45" s="3">
         <v>500</v>
       </c>
       <c r="S45" s="3">
+        <v>500</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E46" s="3">
         <v>50700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>57000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>109400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>54300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>97400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>47500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>51500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>131100</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -2961,73 +3063,79 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1824600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1845700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1888700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1806200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1906100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1870800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1954300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1844900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1788500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1723400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1786600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1834000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1827400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1776600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1775600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1767600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1744300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1638700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1586900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1588600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3058,8 +3166,8 @@
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3091,8 +3199,11 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3318,8 +3438,8 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1880800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1896300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1945700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1915600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1960500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1968300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2001700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1896300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1834800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1854500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1872400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1885700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1874800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1805000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1782700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1789900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1755300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1681300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1614800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1603100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,73 +3661,77 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>36900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3620,17 +3754,17 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>30000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>125000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3661,106 +3795,112 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>19100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>2700</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>10800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>36400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E60" s="3">
         <v>39800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>40500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>65400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>21700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>146800</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3791,73 +3931,79 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1101600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1099800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1099200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1054900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1061700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1060500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1081700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>970200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>976700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>877400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>951300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>950500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>939700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>867400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>822400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>796700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>796000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>716300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>720000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>719400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3888,8 +4034,8 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1122200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1139500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1124900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1076400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1099700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1105200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1122200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1035600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>998400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1024200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>988800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>970800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>969500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>882600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>852200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>848900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>829400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>768300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>736500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>735900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-254400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-262800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-200900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-184600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-164900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-165400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-153500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-175200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-201400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-210700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-161000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-138400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-154800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-137600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-129500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-119000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-129100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-142100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-176800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-191500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>758600</v>
+      </c>
+      <c r="E76" s="3">
         <v>756800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>820800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>839200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>860800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>863100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>879600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>860800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>836400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>830300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>883600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>914900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>905200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>922500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>930500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>941000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>925900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>912900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>878300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>867200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>22400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>51000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>47500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>25100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>77700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>49700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>47200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>31100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5048,8 +5247,8 @@
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E89" s="3">
         <v>6100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-43400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>52000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>96400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-54600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-36000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>65000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-63000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>51900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>29900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5528,8 +5749,8 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,8 +5918,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5723,8 +5953,8 @@
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,73 +6014,77 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E96" s="3">
         <v>2700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>19200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>21900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>19300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>29100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>21200</v>
-      </c>
-      <c r="J96" s="3">
-        <v>18600</v>
       </c>
       <c r="K96" s="3">
         <v>18600</v>
       </c>
       <c r="L96" s="3">
+        <v>18600</v>
+      </c>
+      <c r="M96" s="3">
         <v>33600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-17100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-15900</v>
       </c>
       <c r="P96" s="3">
         <v>-15900</v>
       </c>
       <c r="Q96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="R96" s="3">
         <v>-26500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-10000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-19600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-9700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-21000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-6300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>21300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-32000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-56300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-48500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>13000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>55500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>28400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-10000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>44600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-19400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-27300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6138,8 +6387,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-38700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>40100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-84500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>39100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>13700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-18300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CION_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>CION</t>
   </si>
@@ -656,185 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E8" s="3">
         <v>78700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>52200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>56100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>57900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>59600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>61400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>73600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>60000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>67500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>58500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>54200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>41700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>40400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>74300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>36300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>43400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>38900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35800</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -871,112 +877,118 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>28800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>25800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>31400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19400</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E10" s="3">
         <v>78700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>56100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>57900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>59600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>61400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>58500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>65000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>21500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>42900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>21000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>24000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,47 +1160,50 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E14" s="3">
         <v>2700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-10400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>62000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>13200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>26100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-29200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-17500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>60900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1215,8 +1234,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E17" s="3">
         <v>17600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12700</v>
-      </c>
-      <c r="F17" s="3">
-        <v>13800</v>
       </c>
       <c r="G17" s="3">
         <v>13800</v>
       </c>
       <c r="H17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I17" s="3">
         <v>14500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21900</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E18" s="3">
         <v>61100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>42300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>44000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>46700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>56900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>51500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>44000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>24200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>19600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>36300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>22000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>21400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1517,80 +1550,83 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>-14300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-20600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-11600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>41400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>32100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>9700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E21" s="3">
         <v>61100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>42300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>45100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>46700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>56900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>45800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>51500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>44000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>49200</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1621,47 +1657,50 @@
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E22" s="3">
         <v>22700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19300</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1692,97 +1731,103 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E23" s="3">
         <v>35800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-42700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>51100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>47200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>28000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>34000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>25100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>77700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>49700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>47500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1790,35 +1835,35 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -1826,16 +1871,19 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E26" s="3">
         <v>35900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-42700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>22400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>51000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>47500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>25100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>77700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>49700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>47200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E27" s="3">
         <v>35900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-42700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>22400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>51000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>47500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>34000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>25100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>77700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>49700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>47200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>31100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2369,112 +2438,118 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>14300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>20600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>11600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-41400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-32100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-9700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E33" s="3">
         <v>35900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-42700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>22400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>51000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>47500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>34000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>25100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>77700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>49700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>47200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>31100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E35" s="3">
         <v>35900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-42700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>22400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>51000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>47500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>34000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>25100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>77700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>49700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>47200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>31100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6500</v>
-      </c>
-      <c r="F41" s="3">
-        <v>7700</v>
       </c>
       <c r="G41" s="3">
         <v>7700</v>
       </c>
       <c r="H41" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I41" s="3">
         <v>29800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>96000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>82700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,79 +2976,85 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E43" s="3">
         <v>36400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>78100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>43600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>43100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>40200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2996,8 +3091,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3029,8 +3124,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3067,80 +3165,83 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
-        <v>800</v>
+      <c r="O45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P45" s="3">
         <v>800</v>
       </c>
       <c r="Q45" s="3">
+        <v>800</v>
+      </c>
+      <c r="R45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>500</v>
       </c>
       <c r="T45" s="3">
         <v>500</v>
       </c>
       <c r="U45" s="3">
+        <v>500</v>
+      </c>
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E46" s="3">
         <v>43400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>56200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>57000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>109400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>54300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>97400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>47500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>51500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>46300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>131100</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3171,79 +3272,85 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1813000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1840600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1824600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1845700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1888700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1806200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1906100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1870800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1954300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1844900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1788500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1723400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1786600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1834000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1827400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1776600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1775600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1767600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1744300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1638700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1586900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1588600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1592600</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3280,8 +3387,8 @@
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -3313,8 +3420,11 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3642,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3564,8 +3683,8 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1854800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1883900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1880800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1896300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1945700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1915600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1960500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1968300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2001700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1896300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1834800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1854500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1872400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1885700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1874800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1805000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1782700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1789900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1755300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1681300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1614800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1603100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1599200</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +3922,83 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>10400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>36900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>20100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>41100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3894,17 +4027,17 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>30000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>125000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3935,8 +4068,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3944,109 +4080,112 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2700</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
         <v>2700</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>10800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>36400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E60" s="3">
         <v>32900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>39800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>21500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>44800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>65400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>21700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>146800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4077,79 +4216,85 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1125600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1078500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1101600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1099800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1099200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1054900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1061700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1060500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1081700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>970200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>976700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>877400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>951300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>950500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>939700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>867400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>822400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>796700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>796000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>716300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>720000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>719400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>739900</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4186,8 +4331,8 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -4219,8 +4364,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1147200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1111400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1122200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1139500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1124900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1076400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1099700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1105200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1122200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1035600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>998400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1024200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>988800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>970800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>969500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>882600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>852200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>848900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>829400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>768300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>736500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>735900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>756800</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-296900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-237200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-254400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-262800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-200900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-184600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-164900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-165400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-153500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-175200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-201400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-210700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-161000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-138400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-154800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-137600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-129500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-119000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-129100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-142100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-176800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-191500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-212600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>707600</v>
+      </c>
+      <c r="E76" s="3">
         <v>772500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>758600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>756800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>820800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>839200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>860800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>863100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>879600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>860800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>836400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>830300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>883600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>914900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>905200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>922500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>930500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>941000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>925900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>912900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>878300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>867200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>842400</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E81" s="3">
         <v>35900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-42700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>22400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>51000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>47500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>34000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>25100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>77700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>49700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>47200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>31100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5452,8 +5650,8 @@
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="E89" s="3">
         <v>44400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>43500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-43400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>52000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-16700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>96400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-54600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-36000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>65000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-14600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-63000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>51900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>29900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>64400</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6157,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5976,8 +6196,8 @@
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -6009,8 +6229,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,8 +6377,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6189,8 +6418,8 @@
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -6222,8 +6451,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,79 +6481,83 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E96" s="3">
         <v>18700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>38100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>19200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>21900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>19300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>29100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>21200</v>
-      </c>
-      <c r="L96" s="3">
-        <v>18600</v>
       </c>
       <c r="M96" s="3">
         <v>18600</v>
       </c>
       <c r="N96" s="3">
+        <v>18600</v>
+      </c>
+      <c r="O96" s="3">
         <v>33600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-17100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-17600</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-15900</v>
       </c>
       <c r="R96" s="3">
         <v>-15900</v>
       </c>
       <c r="S96" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="T96" s="3">
         <v>-26500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-10000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-19600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-9700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-21000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +6775,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-47000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-44600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-32000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-56300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>56200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-48500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-25900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>55500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>28400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>44600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-19400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-36200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-27300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-66500</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6642,8 +6890,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6675,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>20000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>40100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-84500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-18300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2000</v>
       </c>
     </row>
